--- a/4 четверть_26_Cursor.xlsx
+++ b/4 четверть_26_Cursor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156DC75B-1E52-49B9-8524-BD442261E9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB56677-167D-48E6-B1BB-7B968CDF378B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7635" yWindow="-18330" windowWidth="23250" windowHeight="12450" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Учебные матриалы" sheetId="7" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="564">
   <si>
     <t>Настройки Cursor</t>
   </si>
@@ -5360,17 +5360,60 @@
 AI:  Archived to openspec/changes/archive/2025-01-23-add-dark-mode/
      Specs updated. Ready for the next feature.</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t># Скопировать папку pptx из репозитория</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+git clone https://github.com/anthropics/skills.git
+cp -r skills/skills/pptx ~/.cursor/skills/pptx</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="50" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5822,9 +5865,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -5832,13 +5875,13 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -5848,7 +5891,7 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -5861,90 +5904,120 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -5952,58 +6025,31 @@
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="47" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="45" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6023,20 +6069,20 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6044,21 +6090,21 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6071,7 +6117,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6153,9 +6199,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2113177</xdr:colOff>
+      <xdr:colOff>2116987</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>1200835</xdr:rowOff>
+      <xdr:rowOff>1197025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -9544,7 +9590,7 @@
       <c r="B10" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="64" t="s">
+      <c r="C10" s="63" t="s">
         <v>470</v>
       </c>
     </row>
@@ -9553,13 +9599,13 @@
       <c r="B11" s="21" t="s">
         <v>471</v>
       </c>
-      <c r="C11" s="64" t="s">
+      <c r="C11" s="63" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="21"/>
-      <c r="C12" s="64"/>
+      <c r="C12" s="63"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
@@ -9643,7 +9689,7 @@
       <c r="B22" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="65" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9691,7 +9737,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="B28" s="66" t="s">
+      <c r="B28" s="65" t="s">
         <v>475</v>
       </c>
       <c r="C28" s="21" t="s">
@@ -9856,7 +9902,7 @@
       <c r="B49" s="21" t="s">
         <v>483</v>
       </c>
-      <c r="C49" s="68" t="s">
+      <c r="C49" s="67" t="s">
         <v>438</v>
       </c>
     </row>
@@ -9881,12 +9927,15 @@
         <v>289</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" s="22" t="s">
         <v>287</v>
       </c>
       <c r="B53" s="35" t="s">
         <v>288</v>
+      </c>
+      <c r="C53" s="87" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -9902,7 +9951,7 @@
       <c r="B55" s="21" t="s">
         <v>482</v>
       </c>
-      <c r="C55" s="68" t="s">
+      <c r="C55" s="67" t="s">
         <v>484</v>
       </c>
     </row>
@@ -10483,7 +10532,7 @@
       <c r="B15" s="59" t="s">
         <v>442</v>
       </c>
-      <c r="C15" s="84" t="s">
+      <c r="C15" s="87" t="s">
         <v>441</v>
       </c>
     </row>
@@ -10534,7 +10583,7 @@
       <c r="C19" s="43" t="s">
         <v>406</v>
       </c>
-      <c r="D19" s="76" t="s">
+      <c r="D19" s="75" t="s">
         <v>404</v>
       </c>
     </row>
@@ -10548,7 +10597,7 @@
       <c r="C20" s="43" t="s">
         <v>408</v>
       </c>
-      <c r="D20" s="84" t="s">
+      <c r="D20" s="83" t="s">
         <v>407</v>
       </c>
     </row>
@@ -10562,7 +10611,7 @@
       <c r="C21" s="49" t="s">
         <v>420</v>
       </c>
-      <c r="D21" s="87" t="s">
+      <c r="D21" s="86" t="s">
         <v>418</v>
       </c>
     </row>
@@ -10610,23 +10659,23 @@
       <c r="D26" s="49"/>
     </row>
     <row r="27" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B27" s="73" t="s">
+      <c r="B27" s="72" t="s">
         <v>501</v>
       </c>
       <c r="C27" s="49"/>
       <c r="D27" s="49"/>
     </row>
     <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="74" t="s">
+      <c r="A28" s="73" t="s">
         <v>502</v>
       </c>
-      <c r="B28" s="73"/>
+      <c r="B28" s="72"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
     </row>
     <row r="29" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B29" s="73"/>
-      <c r="C29" s="75" t="s">
+      <c r="B29" s="72"/>
+      <c r="C29" s="74" t="s">
         <v>504</v>
       </c>
       <c r="D29" s="49"/>
@@ -10643,7 +10692,7 @@
       <c r="B31" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="C31" s="75" t="s">
+      <c r="C31" s="74" t="s">
         <v>494</v>
       </c>
       <c r="D31" s="49"/>
@@ -10653,7 +10702,7 @@
         <v>495</v>
       </c>
       <c r="B32" s="1"/>
-      <c r="C32" s="73"/>
+      <c r="C32" s="72"/>
       <c r="D32" s="49"/>
     </row>
     <row r="33" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -10667,10 +10716,10 @@
       <c r="B34" s="21" t="s">
         <v>499</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="84" t="s">
         <v>505</v>
       </c>
-      <c r="D34" s="73" t="s">
+      <c r="D34" s="72" t="s">
         <v>498</v>
       </c>
     </row>
@@ -10678,7 +10727,7 @@
       <c r="B35" s="21" t="s">
         <v>497</v>
       </c>
-      <c r="C35" s="73" t="s">
+      <c r="C35" s="72" t="s">
         <v>496</v>
       </c>
       <c r="D35" s="49"/>
@@ -10692,10 +10741,10 @@
       <c r="D36" s="49"/>
     </row>
     <row r="37" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="B37" s="70" t="s">
+      <c r="B37" s="69" t="s">
         <v>488</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="76" t="s">
         <v>487</v>
       </c>
       <c r="D37" s="49"/>
@@ -10712,7 +10761,7 @@
       <c r="B39" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="C39" s="65" t="s">
+      <c r="C39" s="64" t="s">
         <v>474</v>
       </c>
       <c r="D39" s="49"/>
@@ -10725,26 +10774,26 @@
       <c r="C40" s="43"/>
     </row>
     <row r="41" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B41" s="71" t="s">
+      <c r="B41" s="70" t="s">
         <v>491</v>
       </c>
-      <c r="C41" s="71" t="s">
+      <c r="C41" s="70" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="106.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="73" t="s">
+      <c r="B42" s="72" t="s">
         <v>503</v>
       </c>
-      <c r="C42" s="73" t="s">
+      <c r="C42" s="72" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B43" s="72" t="s">
+      <c r="B43" s="71" t="s">
         <v>490</v>
       </c>
-      <c r="C43" s="63" t="s">
+      <c r="C43" s="88" t="s">
         <v>383</v>
       </c>
     </row>
@@ -10765,7 +10814,7 @@
       <c r="B46" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="C46" s="69" t="s">
+      <c r="C46" s="68" t="s">
         <v>318</v>
       </c>
       <c r="D46" s="31" t="s">
@@ -10776,7 +10825,7 @@
       <c r="B47" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="C47" s="84" t="s">
+      <c r="C47" s="83" t="s">
         <v>321</v>
       </c>
     </row>
@@ -11099,7 +11148,7 @@
       <c r="B84" s="21" t="s">
         <v>479</v>
       </c>
-      <c r="C84" s="67" t="s">
+      <c r="C84" s="66" t="s">
         <v>478</v>
       </c>
     </row>
@@ -11226,7 +11275,7 @@
     </row>
     <row r="10" spans="1:21" s="38" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="36"/>
-      <c r="C10" s="83" t="s">
+      <c r="C10" s="82" t="s">
         <v>536</v>
       </c>
       <c r="G10" s="36"/>
@@ -11239,7 +11288,7 @@
     </row>
     <row r="11" spans="1:21" s="38" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B11" s="36"/>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="81" t="s">
         <v>557</v>
       </c>
       <c r="G11" s="36"/>
@@ -11251,29 +11300,29 @@
       <c r="U11" s="36"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="79" t="s">
+      <c r="A12" s="78" t="s">
         <v>506</v>
       </c>
       <c r="B12" s="49"/>
       <c r="C12" s="49"/>
-      <c r="D12" s="78"/>
+      <c r="D12" s="77"/>
     </row>
     <row r="13" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="86" t="s">
         <v>507</v>
       </c>
       <c r="B13" s="49"/>
-      <c r="C13" s="78" t="s">
+      <c r="C13" s="77" t="s">
         <v>509</v>
       </c>
       <c r="D13" s="49"/>
     </row>
     <row r="14" spans="1:21" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" s="87" t="s">
+      <c r="A14" s="86" t="s">
         <v>508</v>
       </c>
       <c r="B14" s="49"/>
-      <c r="C14" s="78" t="s">
+      <c r="C14" s="77" t="s">
         <v>510</v>
       </c>
       <c r="D14" s="49"/>
@@ -11283,31 +11332,31 @@
         <v>515</v>
       </c>
       <c r="B15" s="49"/>
-      <c r="C15" s="78"/>
+      <c r="C15" s="77"/>
       <c r="D15" s="49"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="78"/>
+      <c r="A16" s="77"/>
       <c r="B16" s="49"/>
-      <c r="C16" s="78" t="s">
+      <c r="C16" s="77" t="s">
         <v>516</v>
       </c>
       <c r="D16" s="49"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B17" s="78" t="s">
+      <c r="B17" s="77" t="s">
         <v>517</v>
       </c>
-      <c r="C17" s="78" t="s">
+      <c r="C17" s="77" t="s">
         <v>518</v>
       </c>
       <c r="D17" s="49"/>
     </row>
     <row r="18" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="78" t="s">
+      <c r="B18" s="77" t="s">
         <v>519</v>
       </c>
-      <c r="C18" s="78" t="s">
+      <c r="C18" s="77" t="s">
         <v>520</v>
       </c>
       <c r="D18" s="49"/>
@@ -11316,35 +11365,35 @@
       <c r="A19" s="11" t="s">
         <v>537</v>
       </c>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="77"/>
       <c r="D19" s="49"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A20" s="80" t="s">
+      <c r="A20" s="79" t="s">
         <v>535</v>
       </c>
-      <c r="B20" s="78" t="s">
+      <c r="B20" s="77" t="s">
         <v>534</v>
       </c>
-      <c r="C20" s="78"/>
+      <c r="C20" s="77"/>
       <c r="D20" s="49"/>
     </row>
     <row r="21" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="78"/>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78" t="s">
+      <c r="A21" s="77"/>
+      <c r="B21" s="77"/>
+      <c r="C21" s="77" t="s">
         <v>543</v>
       </c>
-      <c r="D21" s="86" t="s">
+      <c r="D21" s="85" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A22" s="80" t="s">
+      <c r="A22" s="79" t="s">
         <v>511</v>
       </c>
-      <c r="B22" s="78" t="s">
+      <c r="B22" s="77" t="s">
         <v>268</v>
       </c>
       <c r="C22" s="49"/>
@@ -11352,29 +11401,29 @@
     </row>
     <row r="23" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" s="49"/>
-      <c r="B23" s="78" t="s">
+      <c r="B23" s="77" t="s">
         <v>513</v>
       </c>
-      <c r="C23" s="78" t="s">
+      <c r="C23" s="77" t="s">
         <v>512</v>
       </c>
-      <c r="D23" s="86" t="s">
+      <c r="D23" s="85" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="49"/>
-      <c r="B24" s="78" t="s">
+      <c r="B24" s="77" t="s">
         <v>514</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="49"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A25" s="80" t="s">
+      <c r="A25" s="79" t="s">
         <v>521</v>
       </c>
-      <c r="B25" s="78" t="s">
+      <c r="B25" s="77" t="s">
         <v>269</v>
       </c>
       <c r="D25" s="49"/>
@@ -11382,7 +11431,7 @@
     <row r="26" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="49"/>
       <c r="B26" s="49"/>
-      <c r="C26" s="78" t="s">
+      <c r="C26" s="77" t="s">
         <v>522</v>
       </c>
       <c r="D26" s="49"/>
@@ -11402,10 +11451,10 @@
       <c r="U26" s="21"/>
     </row>
     <row r="27" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="80" t="s">
+      <c r="A27" s="79" t="s">
         <v>523</v>
       </c>
-      <c r="B27" s="78" t="s">
+      <c r="B27" s="77" t="s">
         <v>271</v>
       </c>
       <c r="C27" s="49"/>
@@ -11428,10 +11477,10 @@
     <row r="28" spans="1:21" s="6" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A28" s="49"/>
       <c r="B28" s="49"/>
-      <c r="C28" s="78" t="s">
+      <c r="C28" s="77" t="s">
         <v>524</v>
       </c>
-      <c r="D28" s="86" t="s">
+      <c r="D28" s="85" t="s">
         <v>561</v>
       </c>
       <c r="F28" s="1"/>
@@ -11452,7 +11501,7 @@
     <row r="29" spans="1:21" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="49"/>
       <c r="B29" s="49"/>
-      <c r="C29" s="78" t="s">
+      <c r="C29" s="77" t="s">
         <v>525</v>
       </c>
       <c r="D29" s="49"/>
@@ -11472,10 +11521,10 @@
       <c r="U29" s="21"/>
     </row>
     <row r="30" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="81" t="s">
+      <c r="A30" s="80" t="s">
         <v>527</v>
       </c>
-      <c r="B30" s="78" t="s">
+      <c r="B30" s="77" t="s">
         <v>533</v>
       </c>
       <c r="C30" s="49"/>
@@ -11497,10 +11546,10 @@
     </row>
     <row r="31" spans="1:21" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="49"/>
-      <c r="B31" s="78" t="s">
+      <c r="B31" s="77" t="s">
         <v>530</v>
       </c>
-      <c r="C31" s="78" t="s">
+      <c r="C31" s="77" t="s">
         <v>529</v>
       </c>
       <c r="D31" s="49"/>
@@ -11520,10 +11569,10 @@
       <c r="U31" s="21"/>
     </row>
     <row r="32" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="81" t="s">
+      <c r="A32" s="80" t="s">
         <v>528</v>
       </c>
-      <c r="B32" s="78" t="s">
+      <c r="B32" s="77" t="s">
         <v>532</v>
       </c>
       <c r="C32" s="49"/>
@@ -11545,13 +11594,13 @@
     </row>
     <row r="33" spans="1:21" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="49"/>
-      <c r="B33" s="78" t="s">
+      <c r="B33" s="77" t="s">
         <v>531</v>
       </c>
-      <c r="C33" s="78" t="s">
+      <c r="C33" s="77" t="s">
         <v>526</v>
       </c>
-      <c r="D33" s="86" t="s">
+      <c r="D33" s="85" t="s">
         <v>562</v>
       </c>
       <c r="F33" s="1"/>
@@ -11592,11 +11641,11 @@
       <c r="U34" s="21"/>
     </row>
     <row r="35" spans="1:21" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="78" t="s">
+      <c r="A35" s="77" t="s">
         <v>539</v>
       </c>
       <c r="B35" s="49"/>
-      <c r="C35" s="78" t="s">
+      <c r="C35" s="77" t="s">
         <v>555</v>
       </c>
       <c r="D35" s="49"/>
@@ -11616,11 +11665,11 @@
       <c r="U35" s="21"/>
     </row>
     <row r="36" spans="1:21" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="78" t="s">
+      <c r="A36" s="77" t="s">
         <v>540</v>
       </c>
       <c r="B36" s="49"/>
-      <c r="C36" s="78" t="s">
+      <c r="C36" s="77" t="s">
         <v>542</v>
       </c>
       <c r="D36" s="49"/>
@@ -11640,11 +11689,11 @@
       <c r="U36" s="21"/>
     </row>
     <row r="37" spans="1:21" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="78" t="s">
+      <c r="A37" s="77" t="s">
         <v>541</v>
       </c>
       <c r="B37" s="49"/>
-      <c r="C37" s="78" t="s">
+      <c r="C37" s="77" t="s">
         <v>556</v>
       </c>
       <c r="D37" s="49"/>
@@ -11686,9 +11735,9 @@
       <c r="U38" s="21"/>
     </row>
     <row r="39" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="78"/>
+      <c r="A39" s="77"/>
       <c r="B39" s="49"/>
-      <c r="C39" s="78" t="s">
+      <c r="C39" s="77" t="s">
         <v>546</v>
       </c>
       <c r="D39" s="49"/>
@@ -11708,7 +11757,7 @@
       <c r="U39" s="21"/>
     </row>
     <row r="40" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="83" t="s">
+      <c r="A40" s="82" t="s">
         <v>545</v>
       </c>
       <c r="B40" s="49"/>
@@ -11731,10 +11780,10 @@
     </row>
     <row r="41" spans="1:21" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A41" s="49"/>
-      <c r="B41" s="78" t="s">
+      <c r="B41" s="77" t="s">
         <v>548</v>
       </c>
-      <c r="C41" s="78" t="s">
+      <c r="C41" s="77" t="s">
         <v>544</v>
       </c>
       <c r="D41" s="49"/>
@@ -11776,13 +11825,13 @@
       <c r="U42" s="21"/>
     </row>
     <row r="43" spans="1:21" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="78" t="s">
+      <c r="A43" s="77" t="s">
         <v>550</v>
       </c>
-      <c r="B43" s="78" t="s">
+      <c r="B43" s="77" t="s">
         <v>554</v>
       </c>
-      <c r="C43" s="78" t="s">
+      <c r="C43" s="77" t="s">
         <v>553</v>
       </c>
       <c r="D43" s="49"/>
@@ -11802,11 +11851,11 @@
       <c r="U43" s="21"/>
     </row>
     <row r="44" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="78" t="s">
+      <c r="A44" s="77" t="s">
         <v>551</v>
       </c>
       <c r="B44" s="49"/>
-      <c r="C44" s="78" t="s">
+      <c r="C44" s="77" t="s">
         <v>552</v>
       </c>
       <c r="D44" s="49"/>

--- a/4 четверть_26_Cursor.xlsx
+++ b/4 четверть_26_Cursor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB56677-167D-48E6-B1BB-7B968CDF378B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45684492-DEE5-4AAB-B812-959318144BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Учебные матриалы" sheetId="7" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="564">
   <si>
     <t>Настройки Cursor</t>
   </si>
@@ -5392,12 +5392,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="50" x14ac:knownFonts="1">
+  <fonts count="51" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5865,9 +5873,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -5875,13 +5883,13 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -5891,7 +5899,7 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -5904,62 +5912,80 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -5968,52 +5994,40 @@
     <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6022,28 +6036,25 @@
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="48" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="48" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="47" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6066,17 +6077,17 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="48" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6087,18 +6098,18 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="48" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6114,10 +6125,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11230,23 +11241,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
+      <c r="A2" s="8" t="s">
+        <v>535</v>
+      </c>
       <c r="B2" s="51"/>
       <c r="C2" s="49"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
+      <c r="A3" s="11" t="s">
+        <v>511</v>
+      </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
+      <c r="A4" s="11" t="s">
+        <v>523</v>
+      </c>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
+      <c r="A5" s="11" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
+      <c r="A6" s="11" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
@@ -11308,7 +11329,7 @@
       <c r="D12" s="77"/>
     </row>
     <row r="13" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="89" t="s">
         <v>507</v>
       </c>
       <c r="B13" s="49"/>
@@ -11318,7 +11339,7 @@
       <c r="D13" s="49"/>
     </row>
     <row r="14" spans="1:21" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" s="86" t="s">
+      <c r="A14" s="89" t="s">
         <v>508</v>
       </c>
       <c r="B14" s="49"/>

--- a/4 четверть_26_Cursor.xlsx
+++ b/4 четверть_26_Cursor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45684492-DEE5-4AAB-B812-959318144BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50487F38-E3BE-4E78-8BF7-2A9F4512080F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Учебные матриалы" sheetId="7" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Prompts" sheetId="4" r:id="rId6"/>
     <sheet name="OpenSpec" sheetId="8" r:id="rId7"/>
     <sheet name="Не программирование Prompts" sheetId="5" r:id="rId8"/>
+    <sheet name="Бонус" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="614">
   <si>
     <t>Настройки Cursor</t>
   </si>
@@ -5387,17 +5388,404 @@
 cp -r skills/skills/pptx ~/.cursor/skills/pptx</t>
     </r>
   </si>
+  <si>
+    <t>Найти репозиторий</t>
+  </si>
+  <si>
+    <t>Пример:
+можно взять Next.js 15 Markdown Boilerplate</t>
+  </si>
+  <si>
+    <t>`https://www.gitsearchai.com/</t>
+  </si>
+  <si>
+    <t>Получить timeline найденного репо</t>
+  </si>
+  <si>
+    <t>`https://gittodoc.com/JiHong88/suneditor</t>
+  </si>
+  <si>
+    <t>Передать url чат агента</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Заменяем в ссылке github на gittodoc</t>
+    </r>
+  </si>
+  <si>
+    <t>Передать промпт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Используем сервис GitSearchAI, чтобы быстро найти подходящий проект на GitHub
+</t>
+  </si>
+  <si>
+    <t>Сделать или добавить функционал  на базе другого проекта</t>
+  </si>
+  <si>
+    <t>Пишем задачу в TraycerAI</t>
+  </si>
+  <si>
+    <t>План генерирует TraycerAI.
+Реализацию делает Cursor.</t>
+  </si>
+  <si>
+    <t>Получим диаграмму и список шагов</t>
+  </si>
+  <si>
+    <t>Передадим план в Cursor.</t>
+  </si>
+  <si>
+    <t>Сгенерируем код.</t>
+  </si>
+  <si>
+    <t>Проведём быстрые проверки качества.</t>
+  </si>
+  <si>
+    <t>Шаг 5</t>
+  </si>
+  <si>
+    <t>Хочу веб приложение Заметки на Markdown.
+Нужны функции.
+1. Список заметок.
+2. Просмотр одной заметки.
+3. Создание и редактирование.
+4. Поиск по тексту.
+5. Теги.
+Ограничения.
+1. Клиент Next.js 15 с App Router и TypeScript.
+2. Стили через Tailwind.
+3. Данные локально в папке content в формате .md.
+4. Нужен план работ. Архитектура. Модули. Очерёдность задач.
+5. Нужен список сущностей. Поля. События. Точки расширения.
+6. Нужны риски и тест кейсы высокого уровня.
+Сформируй результат.
+1. Краткий обзор проекта.
+2. Диаграмма модулей и потоков.
+3. План из шагов с зависимостями.
+4. Список файлов которые надо создать.
+5. Критерии готовности.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Подготовь короткое описание проекта.
+В Cursor создай пустой репозиторий или стартовый шаблон.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> После генерации проверь чтобы были шаги. 
+Артефакты.
+Ясные зависимости. 
+Если чего то не хватает попроси Traycer уточнить.</t>
+    </r>
+  </si>
+  <si>
+    <t>Скопируй план. Вставь в чат Cursor. Попроси следовать строго этому плану. Ниже готовый промпт.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Выступай как сеньор разработчик Next.js и тимлид.
+Вот спецификация из Traycer.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">&lt;ВСТАВЬ_ПЛАН_И_ШАГИ&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Задача.
+Собрать MVP Заметок на Markdown на базе данной спецификации.
+Требования.
+1. Стек Next.js 15 App Router TypeScript Tailwind.
+2. Хранение заметок в папке content как .md.
+3. Страницы. Главная. Просмотр. Создание и редактирование.
+4. Поиск по содержимому. Теги.
+5. Скрипт seed для двух примеров.
+Правила выполнения.
+1. Сначала короткий план действий по шагам.
+2. Затем реализация по шагам.
+3. Создавай файлы целиком. Путь. Имя. Полное содержимое.
+4. Если в плане есть зависимости соблюдай очерёдность.
+5. В конце проверь сборку. Дай команды npm для dev и build. Дай чек лист проверки.
+Если информация из плана неполная задай один уточняющий вопрос и продолжай.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Выступай как сеньор-фулстек разработчик Next.js и архитектор фронтенда.
+У тебя есть документация по проекту по этой ссылке:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">&lt;ССЫЛКА_GITTODOC&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Цель:
+Собрать MVP приложения «Заметки на Markdown».
+Требования:
+1. Стек: Next.js 15, App Router, TypeScript, Tailwind.
+2. Страницы:
+- Главная со списком заметок из папки content.
+- Страница заметки с рендером .md через react-markdown.
+- Форма создания новой заметки с сохранением в content как .md.
+3. Базовая навигация и минимальный стиль.
+4. Скрипт seed для двух примерных заметок.
+5. Команды для запуска dev и build.
+Сделай план работ.
+Выполни шаги последовательно.
+Создай файлы и папки.
+Пиши код целыми файлами.
+Если чего-то не хватает — спроси минимально и продолжай.
+В конце выведи список созданных файлов и инструкции по запуску.</t>
+    </r>
+  </si>
+  <si>
+    <t>Открой сайт TraycerAI</t>
+  </si>
+  <si>
+    <t>`https://traycer.ai/</t>
+  </si>
+  <si>
+    <t>Есть как плагин для курсора</t>
+  </si>
+  <si>
+    <t>ИИ не просто объяснял, а сразу рисовал понятные схемы в цвете</t>
+  </si>
+  <si>
+    <t>1. Открываешь проект в Cursor</t>
+  </si>
+  <si>
+    <t>2. Создаёшь или обновляешь файл .cursor/rules</t>
+  </si>
+  <si>
+    <t>4. Перезапускаешь чат с ассистентом в этом проекте и даёшь обычный запрос</t>
+  </si>
+  <si>
+    <t>3. В блок User добавляешь правило explain with colored mermaid diagrams</t>
+  </si>
+  <si>
+    <t>vibe design уже тут</t>
+  </si>
+  <si>
+    <t>SuperDesign — это open-source дизайн-агент, работающий прямо в IDE: Cursor, Windsurf, VS Code и других. Позволяет генерировать
+UI-компоненты, wireframes и макеты по текстовым описаниям. Поддерживает fork, редактирование, экспорт кода и локальное
+хранение. Архитектура модульная, настройки гибкие.</t>
+  </si>
+  <si>
+    <t>`https://superdesign.dev/</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Далее нажимай Ctrl+Shift+P , введи Superdesign: и выбери Open Canvas View
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Это для того чтобы быстро тестировать варианты интерфейса и править их текстом прямо в Cursor</t>
+    </r>
+  </si>
+  <si>
+    <t>1 В канвасе можно делать вариации и сравнивать их, это удобно: один промпт → сразу несколько вариантов кнопки/секции/темы.</t>
+  </si>
+  <si>
+    <t>2 Есть режим Iterate with feedback: ты кликаешь на элемент в канвасе и пишешь коммент ("сделай фон темнее", "увеличь паддинг") --
+агент перестраивает только нужный кусок, а не весь дизайн</t>
+  </si>
+  <si>
+    <t>3 Канвас помогает сначала собрать скелет (wireframe), а потом уже превращать его в HTML/React-код;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Копируем промпт для курсора
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Шаг 2.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Iterate with feedback 
+</t>
+    </r>
+  </si>
+  <si>
+    <t>rule</t>
+  </si>
+  <si>
+    <t>UI with Cursor</t>
+  </si>
+  <si>
+    <t>Plan -&gt; cursor</t>
+  </si>
+  <si>
+    <t>github -&gt; cursor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пример запроса в чате:
+«Покажи архитектуру простого приложения заметок. Отобрази клиент, сервер, базу данных, и поток создания заметки. Объясни с цветными Mermaid диаграммами»
+</t>
+  </si>
+  <si>
+    <t>`https://superdesign.dev/ - copy prompt</t>
+  </si>
+  <si>
+    <t>`https://www.conventionalcommits.org/ru/v1.0.0/</t>
+  </si>
+  <si>
+    <t>commit</t>
+  </si>
+  <si>
+    <t>дизайн</t>
+  </si>
+  <si>
+    <t>`https://cursor.com/marketplace/figma</t>
+  </si>
+  <si>
+    <t>Самый простой способ добавить skill</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="51" x14ac:knownFonts="1">
+  <fonts count="55" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5805,8 +6193,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5861,6 +6255,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -5873,9 +6273,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -5883,13 +6283,13 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -5899,7 +6299,7 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -5912,146 +6312,155 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="51" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="48" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6068,8 +6477,14 @@
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6077,16 +6492,21 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6098,17 +6518,6 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -6116,7 +6525,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6124,8 +6533,14 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6254,14 +6669,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>707874</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>459908</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3103383</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>1428486</xdr:rowOff>
+      <xdr:colOff>3107193</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1432296</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6298,14 +6713,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>179293</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>56394</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3066220</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>1010203</xdr:rowOff>
+      <xdr:colOff>3070030</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>1006393</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6330,6 +6745,407 @@
         <a:xfrm>
           <a:off x="6331322" y="10388218"/>
           <a:ext cx="2886927" cy="953809"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>98947</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>425822</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3489228</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1043965</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35C944BC-503E-4F36-9625-9A7B2C88193B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6250976" y="2935940"/>
+          <a:ext cx="3399806" cy="608618"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>98947</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>295162</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3032750</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1202614</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E10662E-25B0-4CCF-B2E9-E5C5D87BAD1D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2788359" y="9360721"/>
+          <a:ext cx="2929993" cy="911262"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>162828</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>41013</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1884271</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1164438</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Рисунок 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1404CCD0-1BE3-41DE-B112-70A394479620}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6314857" y="17309278"/>
+          <a:ext cx="1730968" cy="1131045"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>171897</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>282515</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1812091</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>860217</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Рисунок 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12810AE3-1970-4F92-9C2B-7F96569D5100}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11209691" y="20632397"/>
+          <a:ext cx="1645909" cy="583417"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>125170</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>32877</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1924647</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1044190</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Рисунок 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE3A6641-28B6-4A32-9302-5C5B48C25A7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6277199" y="21301642"/>
+          <a:ext cx="1791857" cy="1005598"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2501463</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>15015</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>4400671</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1050655</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Рисунок 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0472A9A0-AD7D-46EC-A880-84D638787C4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8653492" y="21283780"/>
+          <a:ext cx="1883968" cy="1045165"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>168087</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>49505</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2226256</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>1012115</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Рисунок 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B108EB2-15AA-49EA-9F34-22B48EB14BAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6320116" y="23682711"/>
+          <a:ext cx="2058169" cy="972135"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>50538</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>65097</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2554942</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>894007</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Рисунок 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BC197A9-BBC6-4D67-A933-7085B7971E5A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2739950" y="20414979"/>
+          <a:ext cx="2504404" cy="836530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>105573</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>253927</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2607384</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1045423</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Рисунок 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19029F13-25DE-4EE1-A5F6-2C7D2611BAA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2794985" y="22979456"/>
+          <a:ext cx="2494191" cy="780066"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9743,7 +10559,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="31" t="s">
         <v>135</v>
       </c>
     </row>
@@ -10417,7 +11233,7 @@
     <tabColor rgb="FF00B050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:U95"/>
+  <dimension ref="A2:U97"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.109375" style="1" customWidth="1"/>
@@ -10559,641 +11375,660 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="B17" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43" t="s">
-        <v>400</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="C17" s="93" t="s">
+        <v>609</v>
+      </c>
+      <c r="D17" s="21"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="94" t="s">
+        <v>612</v>
+      </c>
+      <c r="D18" s="21"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C18" s="43" t="s">
+      <c r="C20" s="43" t="s">
         <v>403</v>
       </c>
-      <c r="D18" s="43" t="s">
+      <c r="D20" s="43" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="52" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="52" t="s">
         <v>423</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="C21" s="43" t="s">
         <v>406</v>
       </c>
-      <c r="D19" s="75" t="s">
+      <c r="D21" s="75" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="50" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="50" t="s">
         <v>421</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C22" s="43" t="s">
         <v>408</v>
       </c>
-      <c r="D20" s="83" t="s">
+      <c r="D22" s="83" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="50" t="s">
+    <row r="23" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="50" t="s">
         <v>421</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C21" s="49" t="s">
+      <c r="C23" s="49" t="s">
         <v>420</v>
       </c>
-      <c r="D21" s="86" t="s">
+      <c r="D23" s="86" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="50" t="s">
+    <row r="24" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="50" t="s">
         <v>422</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="C24" s="56" t="s">
         <v>461</v>
       </c>
-      <c r="D22" s="53" t="s">
+      <c r="D24" s="53" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C25" s="49" t="s">
         <v>416</v>
       </c>
-      <c r="D23" s="49" t="s">
+      <c r="D25" s="49" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="1"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B25" s="1"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-    </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
-        <v>500</v>
-      </c>
       <c r="B26" s="1"/>
       <c r="C26" s="49"/>
       <c r="D26" s="49"/>
     </row>
-    <row r="27" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B27" s="72" t="s">
-        <v>501</v>
-      </c>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="1"/>
       <c r="C27" s="49"/>
       <c r="D27" s="49"/>
     </row>
-    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="73" t="s">
-        <v>502</v>
-      </c>
-      <c r="B28" s="72"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B28" s="1"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
     </row>
     <row r="29" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B29" s="72"/>
-      <c r="C29" s="74" t="s">
-        <v>504</v>
-      </c>
+      <c r="B29" s="72" t="s">
+        <v>501</v>
+      </c>
+      <c r="C29" s="49"/>
       <c r="D29" s="49"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="61" t="s">
-        <v>492</v>
-      </c>
-      <c r="B30" s="1"/>
+    <row r="30" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="73" t="s">
+        <v>502</v>
+      </c>
+      <c r="B30" s="72"/>
       <c r="C30" s="49"/>
       <c r="D30" s="49"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="1" t="s">
-        <v>493</v>
-      </c>
+    <row r="31" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B31" s="72"/>
       <c r="C31" s="74" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="D31" s="49"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="61" t="s">
+        <v>492</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="49"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C33" s="74" t="s">
+        <v>494</v>
+      </c>
+      <c r="D33" s="49"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="61" t="s">
         <v>495</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="49"/>
-    </row>
-    <row r="33" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B33" s="1"/>
-      <c r="C33" s="21" t="s">
+      <c r="B34" s="1"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="49"/>
+    </row>
+    <row r="35" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B35" s="1"/>
+      <c r="C35" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="D33" s="49"/>
-    </row>
-    <row r="34" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B34" s="21" t="s">
+      <c r="D35" s="49"/>
+    </row>
+    <row r="36" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B36" s="21" t="s">
         <v>499</v>
       </c>
-      <c r="C34" s="84" t="s">
+      <c r="C36" s="84" t="s">
         <v>505</v>
       </c>
-      <c r="D34" s="72" t="s">
+      <c r="D36" s="72" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B35" s="21" t="s">
+    <row r="37" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B37" s="21" t="s">
         <v>497</v>
       </c>
-      <c r="C35" s="72" t="s">
+      <c r="C37" s="72" t="s">
         <v>496</v>
       </c>
-      <c r="D35" s="49"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="61" t="s">
+      <c r="D37" s="49"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="61" t="s">
         <v>486</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="49"/>
-    </row>
-    <row r="37" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="B37" s="69" t="s">
-        <v>488</v>
-      </c>
-      <c r="C37" s="76" t="s">
-        <v>487</v>
-      </c>
-      <c r="D37" s="49"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
-        <v>472</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="49"/>
       <c r="D38" s="49"/>
     </row>
-    <row r="39" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="39" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="B39" s="69" t="s">
+        <v>488</v>
+      </c>
+      <c r="C39" s="76" t="s">
+        <v>487</v>
+      </c>
+      <c r="D39" s="49"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="49"/>
+    </row>
+    <row r="41" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="C39" s="64" t="s">
+      <c r="C41" s="64" t="s">
         <v>474</v>
       </c>
-      <c r="D39" s="49"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="61" t="s">
+      <c r="D41" s="49"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="61" t="s">
         <v>380</v>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="43"/>
-    </row>
-    <row r="41" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B41" s="70" t="s">
+      <c r="B42" s="1"/>
+      <c r="C42" s="43"/>
+    </row>
+    <row r="43" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B43" s="70" t="s">
         <v>491</v>
       </c>
-      <c r="C41" s="70" t="s">
+      <c r="C43" s="70" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="106.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="72" t="s">
+    <row r="44" spans="1:4" ht="106.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="72" t="s">
         <v>503</v>
       </c>
-      <c r="C42" s="72" t="s">
+      <c r="C44" s="72" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B43" s="71" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B45" s="71" t="s">
         <v>490</v>
       </c>
-      <c r="C43" s="88" t="s">
+      <c r="C45" s="88" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C44" s="44" t="s">
+      <c r="C46" s="44" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="B46" s="21" t="s">
+    <row r="48" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="B48" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C48" s="68" t="s">
         <v>318</v>
       </c>
-      <c r="D46" s="31" t="s">
+      <c r="D48" s="31" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="B47" s="21" t="s">
+    <row r="49" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="B49" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="C47" s="83" t="s">
+      <c r="C49" s="83" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="13" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C48" s="44"/>
-    </row>
-    <row r="49" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B49" s="21" t="s">
+      <c r="C50" s="44"/>
+    </row>
+    <row r="51" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B51" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="C49" s="44" t="s">
+      <c r="C51" s="44" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="62" t="s">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="62" t="s">
         <v>325</v>
       </c>
-      <c r="B50" s="21" t="s">
+      <c r="B52" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="C50" s="44"/>
-    </row>
-    <row r="51" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="44"/>
-      <c r="B51" s="21" t="s">
+      <c r="C52" s="44"/>
+    </row>
+    <row r="53" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="44"/>
+      <c r="B53" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="C51" s="55" t="s">
+      <c r="C53" s="55" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B52" s="21" t="s">
+    <row r="54" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B54" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="C52" s="44" t="s">
+      <c r="C54" s="44" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="8" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C53" s="44"/>
-    </row>
-    <row r="54" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B54" s="53" t="s">
+      <c r="C55" s="44"/>
+    </row>
+    <row r="56" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B56" s="53" t="s">
         <v>439</v>
       </c>
-      <c r="C54" s="54" t="s">
+      <c r="C56" s="54" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A55" s="21" t="s">
+    <row r="57" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A57" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="B55" s="53" t="s">
+      <c r="B57" s="53" t="s">
         <v>440</v>
       </c>
-      <c r="C55" s="54" t="s">
+      <c r="C57" s="54" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A56" s="21" t="s">
+    <row r="58" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A58" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="B56" s="43" t="s">
+      <c r="B58" s="43" t="s">
         <v>385</v>
       </c>
-      <c r="C56" s="44" t="s">
+      <c r="C58" s="44" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="8" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="C57" s="44"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B58" s="21" t="s">
+      <c r="C59" s="44"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B60" s="21" t="s">
         <v>390</v>
       </c>
-      <c r="C58" s="44" t="s">
+      <c r="C60" s="44" t="s">
         <v>392</v>
       </c>
-      <c r="D58" s="47" t="s">
+      <c r="D60" s="47" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B59" s="21" t="s">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B61" s="21" t="s">
         <v>393</v>
       </c>
-      <c r="C59" s="44" t="s">
+      <c r="C61" s="44" t="s">
         <v>395</v>
       </c>
-      <c r="D59" s="47" t="s">
+      <c r="D61" s="47" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="8" t="s">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="C60" s="44"/>
-    </row>
-    <row r="61" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="52"/>
-      <c r="B61" s="21" t="s">
+      <c r="C62" s="44"/>
+    </row>
+    <row r="63" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="52"/>
+      <c r="B63" s="21" t="s">
         <v>425</v>
       </c>
-      <c r="C61" s="52" t="s">
+      <c r="C63" s="52" t="s">
         <v>427</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
+    <row r="64" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B62" s="43" t="s">
+      <c r="B64" s="43" t="s">
         <v>343</v>
       </c>
-      <c r="C62" s="44" t="s">
+      <c r="C64" s="44" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
+    <row r="65" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B63" s="43" t="s">
+      <c r="B65" s="43" t="s">
         <v>346</v>
       </c>
-      <c r="C63" s="44" t="s">
+      <c r="C65" s="44" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
+    <row r="66" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B64" s="17" t="s">
+      <c r="B66" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="C64" s="44" t="s">
+      <c r="C66" s="44" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="43" t="s">
+    <row r="67" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="43" t="s">
         <v>339</v>
       </c>
-      <c r="B65" s="45" t="s">
+      <c r="B67" s="45" t="s">
         <v>344</v>
       </c>
-      <c r="C65" s="44" t="s">
+      <c r="C67" s="44" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="43" t="s">
+    <row r="68" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A68" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="B66" s="43" t="s">
+      <c r="B68" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="C66" s="44" t="s">
+      <c r="C68" s="44" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="8" t="s">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-    </row>
-    <row r="68" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B68" s="43" t="s">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+    </row>
+    <row r="70" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B70" s="43" t="s">
         <v>356</v>
       </c>
-      <c r="C68" s="44" t="s">
+      <c r="C70" s="44" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="B69" s="43" t="s">
+    <row r="71" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="B71" s="43" t="s">
         <v>352</v>
       </c>
-      <c r="C69" s="43" t="s">
+      <c r="C71" s="43" t="s">
         <v>350</v>
       </c>
-      <c r="D69" s="43" t="s">
+      <c r="D71" s="43" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="8" t="s">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="8" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B71" s="17" t="s">
+    <row r="73" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B73" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="C71" s="44" t="s">
+      <c r="C73" s="44" t="s">
         <v>357</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="46" t="s">
-        <v>360</v>
-      </c>
-      <c r="B72" s="1"/>
-      <c r="C72" s="43"/>
-    </row>
-    <row r="73" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B73" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="C73" s="44" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="46" t="s">
-        <v>364</v>
-      </c>
-      <c r="C74" s="44"/>
-    </row>
-    <row r="75" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+      <c r="B74" s="1"/>
+      <c r="C74" s="43"/>
+    </row>
+    <row r="75" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B75" s="21" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C75" s="44" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="46" t="s">
+        <v>364</v>
+      </c>
+      <c r="C76" s="44"/>
+    </row>
+    <row r="77" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B77" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="C77" s="44" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="46" t="s">
         <v>367</v>
       </c>
-      <c r="C76" s="44"/>
-    </row>
-    <row r="77" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="21"/>
-      <c r="B77" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="C77" s="44" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="21"/>
-      <c r="B78" s="48" t="s">
-        <v>373</v>
-      </c>
-      <c r="C78" s="44" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C78" s="44"/>
+    </row>
+    <row r="79" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A79" s="21"/>
       <c r="B79" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="C79" s="44" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="21"/>
+      <c r="B80" s="48" t="s">
+        <v>373</v>
+      </c>
+      <c r="C80" s="44" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="21"/>
+      <c r="B81" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="C79" s="44" t="s">
+      <c r="C81" s="44" t="s">
         <v>371</v>
       </c>
-      <c r="D79" s="47" t="s">
+      <c r="D81" s="47" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="21"/>
-      <c r="B80" s="21" t="s">
+    <row r="82" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="21"/>
+      <c r="B82" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="C80" s="44" t="s">
+      <c r="C82" s="44" t="s">
         <v>375</v>
       </c>
-      <c r="D80" s="44"/>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="46" t="s">
+      <c r="D82" s="44"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="46" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A82" s="1" t="s">
+    <row r="84" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B82" s="21" t="s">
+      <c r="B84" s="21" t="s">
         <v>480</v>
       </c>
-      <c r="C82" s="44" t="s">
+      <c r="C84" s="44" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B83" s="21" t="s">
+    <row r="85" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B85" s="21" t="s">
         <v>477</v>
       </c>
-      <c r="C83" s="44" t="s">
+      <c r="C85" s="44" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="B84" s="21" t="s">
+    <row r="86" spans="1:4" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="B86" s="21" t="s">
         <v>479</v>
       </c>
-      <c r="C84" s="66" t="s">
+      <c r="C86" s="66" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="13" t="s">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="13" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B86" s="21" t="s">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B88" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="C86" s="44" t="s">
+      <c r="C88" s="44" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C90" s="43"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C91" s="43"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C92" s="43"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C93" s="43"/>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C94" s="43"/>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C95" s="43"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C96" s="43"/>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C97" s="43"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D46" r:id="rId1" xr:uid="{28B9BCE7-45B7-4868-B75C-CE16E91A776C}"/>
+    <hyperlink ref="D48" r:id="rId1" xr:uid="{28B9BCE7-45B7-4868-B75C-CE16E91A776C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
@@ -12894,4 +13729,326 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31EEDDA-903A-41FC-9D3A-52F6110D8B65}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:U43"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="39.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="21" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="76.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="21" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="6" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="6" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="21" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="21" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="21" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="7" customWidth="1"/>
+    <col min="21" max="21" width="67.77734375" style="21" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="8.77734375" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="92" t="s">
+        <v>573</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>606</v>
+      </c>
+      <c r="C2" s="49"/>
+    </row>
+    <row r="3" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="92" t="s">
+        <v>575</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>605</v>
+      </c>
+      <c r="C3" s="15"/>
+    </row>
+    <row r="4" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="92" t="s">
+        <v>589</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>603</v>
+      </c>
+      <c r="C4" s="15"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="92" t="s">
+        <v>594</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="21"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="U7" s="4"/>
+    </row>
+    <row r="8" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="92" t="s">
+        <v>573</v>
+      </c>
+      <c r="C8" s="49"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="91" t="s">
+        <v>564</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B10" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="C10" s="90" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="91" t="s">
+        <v>567</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B12" s="90" t="s">
+        <v>570</v>
+      </c>
+      <c r="C12" s="90" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="91" t="s">
+        <v>571</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="C14" s="90" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C15" s="90"/>
+    </row>
+    <row r="16" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="92" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="C17" s="90" t="s">
+        <v>586</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="288" x14ac:dyDescent="0.3">
+      <c r="B18" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="C18" s="90" t="s">
+        <v>582</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="288" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="C20" s="90" t="s">
+        <v>583</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="92" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B26" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="21" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B28" s="21" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B29" s="21" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="92" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A32" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="C32" s="90" t="s">
+        <v>595</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="C33" s="90"/>
+    </row>
+    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C34" s="90" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B35" s="90" t="s">
+        <v>602</v>
+      </c>
+      <c r="C35" s="90" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C36" s="90" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="54" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/4 четверть_26_Cursor.xlsx
+++ b/4 четверть_26_Cursor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50487F38-E3BE-4E78-8BF7-2A9F4512080F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D608C09E-487C-43CF-9CCE-C835B07D187E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3990" yWindow="-17730" windowWidth="28770" windowHeight="15270" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Учебные матриалы" sheetId="7" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="616">
   <si>
     <t>Настройки Cursor</t>
   </si>
@@ -5751,17 +5751,31 @@
   <si>
     <t>Самый простой способ добавить skill</t>
   </si>
+  <si>
+    <t>java и kotlin</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/companies/selectel/news/1096778/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="55" x14ac:knownFonts="1">
+  <fonts count="56" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6273,7 +6287,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -6283,13 +6297,13 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6299,7 +6313,7 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6312,62 +6326,80 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="52" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6376,52 +6408,40 @@
     <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6430,28 +6450,25 @@
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="52" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="52" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="51" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6474,17 +6491,17 @@
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="52" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6495,18 +6512,18 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="52" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6522,15 +6539,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6539,10 +6553,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6762,13 +6776,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>98947</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>425822</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3489228</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>1043965</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6806,13 +6820,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>98947</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>295162</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>3032750</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>1202614</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6850,13 +6864,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>162828</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>41013</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1884271</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>1164438</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6894,13 +6908,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>171897</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>282515</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1812091</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>860217</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6938,13 +6952,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>125170</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>32877</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1924647</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>1044190</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6982,13 +6996,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2501463</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>15015</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>4400671</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>1050655</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7026,13 +7040,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>168087</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>49505</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2226256</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>1012115</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7070,13 +7084,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>50538</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>65097</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>2554942</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>894007</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7114,13 +7128,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>105573</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>253927</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>2607384</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>1045423</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -13736,7 +13750,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:U43"/>
+  <dimension ref="A2:U44"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.109375" style="1" customWidth="1"/>
@@ -13805,250 +13819,262 @@
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="21"/>
+      <c r="A6" s="92" t="s">
+        <v>614</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>615</v>
+      </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="U7" s="4"/>
-    </row>
-    <row r="8" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="92" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="31"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="U8" s="4"/>
+    </row>
+    <row r="9" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="92" t="s">
         <v>573</v>
       </c>
-      <c r="C8" s="49"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="91" t="s">
+      <c r="C9" s="49"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="91" t="s">
         <v>564</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B10" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B10" s="21" t="s">
+    <row r="11" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B11" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="C10" s="90" t="s">
+      <c r="C11" s="90" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="91" t="s">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="91" t="s">
         <v>567</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B12" s="21" t="s">
         <v>269</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B12" s="90" t="s">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B13" s="90" t="s">
         <v>570</v>
       </c>
-      <c r="C12" s="90" t="s">
+      <c r="C13" s="90" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="91" t="s">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="91" t="s">
         <v>571</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B14" s="21" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="C14" s="90" t="s">
+    <row r="15" spans="1:21" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="C15" s="90" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="C15" s="90"/>
-    </row>
-    <row r="16" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="92" t="s">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C16" s="90"/>
+    </row>
+    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="92" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B18" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="C17" s="90" t="s">
+      <c r="C18" s="90" t="s">
         <v>586</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="288" x14ac:dyDescent="0.3">
-      <c r="B18" s="21" t="s">
+    <row r="19" spans="1:4" ht="288" x14ac:dyDescent="0.3">
+      <c r="B19" s="21" t="s">
         <v>588</v>
       </c>
-      <c r="C18" s="90" t="s">
+      <c r="C19" s="90" t="s">
         <v>582</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D19" s="21" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B20" s="21" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="288" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:4" ht="288" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B21" s="21" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="90" t="s">
+      <c r="C21" s="90" t="s">
         <v>583</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D21" s="21" t="s">
         <v>584</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B23" s="21" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="92" t="s">
+    <row r="26" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="92" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B26" s="21" t="s">
+    <row r="27" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B27" s="21" t="s">
         <v>590</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D27" s="21" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="21" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B28" s="21" t="s">
         <v>591</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B28" s="21" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B29" s="21" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B30" s="21" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="92" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="92" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A32" s="22" t="s">
+    <row r="33" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A33" s="22" t="s">
         <v>268</v>
       </c>
-      <c r="C32" s="90" t="s">
+      <c r="C33" s="90" t="s">
         <v>595</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="22" t="s">
+    <row r="34" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B34" s="21" t="s">
         <v>597</v>
       </c>
-      <c r="C33" s="90"/>
-    </row>
-    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="90"/>
+    </row>
+    <row r="35" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C35" s="90" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B35" s="90" t="s">
+    <row r="36" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B36" s="90" t="s">
         <v>602</v>
       </c>
-      <c r="C35" s="90" t="s">
+      <c r="C36" s="90" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C36" s="90" t="s">
+    <row r="37" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C37" s="90" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="22" t="s">
+    <row r="38" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B38" s="21" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="10" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="54" type="noConversion"/>
+  <phoneticPr fontId="55" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{6DBA74A1-9844-4CC6-9CBF-7A0CDA3E39DB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/4 четверть_26_Cursor.xlsx
+++ b/4 четверть_26_Cursor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D608C09E-487C-43CF-9CCE-C835B07D187E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74728E2-FA42-4801-B506-81909A936E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3990" yWindow="-17730" windowWidth="28770" windowHeight="15270" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3990" yWindow="-17730" windowWidth="28770" windowHeight="15270" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Учебные матриалы" sheetId="7" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="617">
   <si>
     <t>Настройки Cursor</t>
   </si>
@@ -5756,6 +5756,10 @@
   </si>
   <si>
     <t>https://habr.com/ru/companies/selectel/news/1096778/</t>
+  </si>
+  <si>
+    <t>https://github.com/unclebob/ub-mode
+Скилы от мегапрограммиста, автора "чистый код".</t>
   </si>
 </sst>
 </file>
@@ -6688,9 +6692,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3107193</xdr:colOff>
+      <xdr:colOff>3103383</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>1432296</xdr:rowOff>
+      <xdr:rowOff>1428486</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6732,9 +6736,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3070030</xdr:colOff>
+      <xdr:colOff>3066220</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>1006393</xdr:rowOff>
+      <xdr:rowOff>1010203</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -11306,6 +11310,7 @@
       <c r="A6" s="62" t="s">
         <v>325</v>
       </c>
+      <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
@@ -11378,6 +11383,9 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="53" t="s">
+        <v>616</v>
+      </c>
       <c r="B16" s="1" t="s">
         <v>396</v>
       </c>
@@ -12043,10 +12051,11 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D48" r:id="rId1" xr:uid="{28B9BCE7-45B7-4868-B75C-CE16E91A776C}"/>
+    <hyperlink ref="A16" r:id="rId2" xr:uid="{89BCDF7F-2D48-42C1-AA18-10CD67F98341}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
